--- a/results/feature_selection/global_ind/wnp/rP_calc/metrics_global.xlsx
+++ b/results/feature_selection/global_ind/wnp/rP_calc/metrics_global.xlsx
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>Ridge_w</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -496,110 +496,110 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>X_calc, V_calc, dVdt_calc, Xlag1_calc</t>
+          <t>P, Plag1, mu_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.5024066732742092</v>
+        <v>0.9522453267938643</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08463034088669874</v>
+        <v>0.03130820189787992</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02207180159605955</v>
+        <v>0.002196811014544803</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1485658157048907</v>
+        <v>0.04687015057096364</v>
       </c>
       <c r="H2" t="n">
-        <v>397.3001448997037</v>
+        <v>209.1750282508051</v>
       </c>
       <c r="I2" t="n">
-        <v>0.166728259134979</v>
+        <v>0.01786416967202207</v>
       </c>
       <c r="J2" t="n">
-        <v>-197.9265392767067</v>
+        <v>-310.2789224710634</v>
       </c>
       <c r="K2" t="n">
-        <v>-189.9706030904496</v>
+        <v>-302.4739475967377</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>elasticnet_w</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>X_calc, V_calc, Xlag1_calc</t>
+          <t>P, Plag1, mu_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4623209673919972</v>
+        <v>0.9516912090509422</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08919638477841117</v>
+        <v>0.03168055529648763</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02384988763449581</v>
+        <v>0.002222301545194057</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1544340883176244</v>
+        <v>0.04714129341876458</v>
       </c>
       <c r="H3" t="n">
-        <v>459.5255607637866</v>
+        <v>219.5073167429236</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1794986311265479</v>
+        <v>0.01804824836635319</v>
       </c>
       <c r="J3" t="n">
-        <v>-195.7426917420421</v>
+        <v>-309.6790181793334</v>
       </c>
       <c r="K3" t="n">
-        <v>-189.7757396023493</v>
+        <v>-301.8740433050077</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>LASSO_w</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T, X_calc, V_calc, Xlag1_calc</t>
+          <t>P, Plag1, Xlag1_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4009951474270022</v>
+        <v>0.9481307406623936</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08341278472084158</v>
+        <v>0.03246862689752666</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02657012373550958</v>
+        <v>0.002386090252094839</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1630034470049931</v>
+        <v>0.04884762278857425</v>
       </c>
       <c r="H4" t="n">
-        <v>352.6237278724161</v>
+        <v>326.0256158416253</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2003005423867561</v>
+        <v>0.01873104097774832</v>
       </c>
       <c r="J4" t="n">
-        <v>-187.9102645619405</v>
+        <v>-307.9811547772856</v>
       </c>
       <c r="K4" t="n">
-        <v>-179.9543283756834</v>
+        <v>-302.1274236215413</v>
       </c>
     </row>
     <row r="5">
@@ -609,153 +609,153 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>X_calc, V_calc, Xlag1_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.2437747527178186</v>
+        <v>0.9476184290006716</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1028535840408041</v>
+        <v>0.03423563979216381</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03354396597272183</v>
+        <v>0.002409657618925982</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1831501186806108</v>
+        <v>0.04908826355582342</v>
       </c>
       <c r="H5" t="n">
-        <v>1517.440554345099</v>
+        <v>271.7919564830427</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2518483503655597</v>
+        <v>0.01840123163304671</v>
       </c>
       <c r="J5" t="n">
-        <v>-177.32450731016</v>
+        <v>-309.4700716372012</v>
       </c>
       <c r="K5" t="n">
-        <v>-171.3575551704671</v>
+        <v>-305.5675842000383</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ridge_w</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>P, T, Plag1</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.2212961873222195</v>
+        <v>0.9052990221656849</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08722389234352643</v>
+        <v>0.03500191050081443</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03454105015558331</v>
+        <v>0.00435643544866426</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1858522266629682</v>
+        <v>0.06600329877107855</v>
       </c>
       <c r="H6" t="n">
-        <v>1038.78173116383</v>
+        <v>259.8660883615503</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2602898789122425</v>
+        <v>0.03295979816435951</v>
       </c>
       <c r="J6" t="n">
-        <v>-171.7427673449679</v>
+        <v>-276.6772579097751</v>
       </c>
       <c r="K6" t="n">
-        <v>-161.7978471121465</v>
+        <v>-270.8235267540308</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LASSO_w</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>P, Plag1, X_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.2166690539506936</v>
+        <v>0.8282722573775927</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08749167395818683</v>
+        <v>0.05246073598394848</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0347462964164342</v>
+        <v>0.00789982154976508</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1864035847735612</v>
+        <v>0.08888094030648573</v>
       </c>
       <c r="H7" t="n">
-        <v>1048.554691693007</v>
+        <v>684.7418288585025</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2618216913062959</v>
+        <v>0.05854819787155776</v>
       </c>
       <c r="J7" t="n">
-        <v>-171.4228436921574</v>
+        <v>-245.7275856368842</v>
       </c>
       <c r="K7" t="n">
-        <v>-161.477923459336</v>
+        <v>-239.87385448114</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>elasticnet_w</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2087970255585189</v>
+        <v>0.7417510664890572</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09124007137070149</v>
+        <v>0.06740423472960835</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03509547684048434</v>
+        <v>0.01187997034724544</v>
       </c>
       <c r="G8" t="n">
-        <v>0.187337868143321</v>
+        <v>0.1089952767198902</v>
       </c>
       <c r="H8" t="n">
-        <v>1151.295119165252</v>
+        <v>1097.556805203604</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2644277261207834</v>
+        <v>0.08629065929635467</v>
       </c>
       <c r="J8" t="n">
-        <v>-170.8828831749095</v>
+        <v>-228.510875975841</v>
       </c>
       <c r="K8" t="n">
-        <v>-160.9379629420881</v>
+        <v>-226.5596322572596</v>
       </c>
     </row>
     <row r="9">
@@ -769,32 +769,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FS_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.11223158145152</v>
+        <v>0.7143882502389979</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09620445572736631</v>
+        <v>0.06867649567441483</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04933537786007672</v>
+        <v>0.01313871492848514</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2221156857587431</v>
+        <v>0.1146242336004265</v>
       </c>
       <c r="H9" t="n">
-        <v>791.9057773292428</v>
+        <v>927.9502745936268</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7374084778750195</v>
+        <v>0.09538062537824026</v>
       </c>
       <c r="J9" t="n">
-        <v>-160.4921479883014</v>
+        <v>-223.2739875957616</v>
       </c>
       <c r="K9" t="n">
-        <v>-158.5031639417371</v>
+        <v>-221.3227438771802</v>
       </c>
     </row>
     <row r="10">
@@ -808,32 +808,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FS_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.1587030023597507</v>
+        <v>0.6801001755884444</v>
       </c>
       <c r="E10" t="n">
-        <v>0.09793219675146768</v>
+        <v>0.08556164177400588</v>
       </c>
       <c r="F10" t="n">
-        <v>0.05139671575808008</v>
+        <v>0.01471603532464256</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2267084377743362</v>
+        <v>0.1213096670700343</v>
       </c>
       <c r="H10" t="n">
-        <v>691.6259078043272</v>
+        <v>1838.478875739901</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7681772034771627</v>
+        <v>0.1067711720507165</v>
       </c>
       <c r="J10" t="n">
-        <v>-158.2817742332603</v>
+        <v>-217.378512148551</v>
       </c>
       <c r="K10" t="n">
-        <v>-156.292790186696</v>
+        <v>-215.4272684299695</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/global_ind/wnp/rP_calc/metrics_global.xlsx
+++ b/results/feature_selection/global_ind/wnp/rP_calc/metrics_global.xlsx
@@ -488,118 +488,118 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ridge_w</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P, Plag1, mu_calc, dXdt_calc</t>
+          <t>X_calc, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9522453267938643</v>
+        <v>0.4318110137008908</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03130820189787992</v>
+        <v>0.0948677121088215</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002196811014544803</v>
+        <v>0.02613783614552213</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04687015057096364</v>
+        <v>0.1616720017366091</v>
       </c>
       <c r="H2" t="n">
-        <v>209.1750282508051</v>
+        <v>493.2972475594083</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01786416967202207</v>
+        <v>0.1902531811915983</v>
       </c>
       <c r="J2" t="n">
-        <v>-310.2789224710634</v>
+        <v>-183.5073103897618</v>
       </c>
       <c r="K2" t="n">
-        <v>-302.4739475967377</v>
+        <v>-177.6535792340175</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>elasticnet_w</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P, Plag1, mu_calc, dXdt_calc</t>
+          <t>V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9516912090509422</v>
+        <v>0.4106856492401957</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03168055529648763</v>
+        <v>0.09130340515348176</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002222301545194057</v>
+        <v>0.02710964539931398</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04714129341876458</v>
+        <v>0.1646500695393536</v>
       </c>
       <c r="H3" t="n">
-        <v>219.5073167429236</v>
+        <v>1386.078889000424</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01804824836635319</v>
+        <v>0.1967710570074611</v>
       </c>
       <c r="J3" t="n">
-        <v>-309.6790181793334</v>
+        <v>-183.6090161725872</v>
       </c>
       <c r="K3" t="n">
-        <v>-301.8740433050077</v>
+        <v>-179.7065287354244</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LASSO_w</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>P, Plag1, Xlag1_calc</t>
+          <t>T, X_calc, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9481307406623936</v>
+        <v>0.4037051313929886</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03246862689752666</v>
+        <v>0.08387228943373816</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002386090252094839</v>
+        <v>0.02743076325992162</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04884762278857425</v>
+        <v>0.165622351329528</v>
       </c>
       <c r="H4" t="n">
-        <v>326.0256158416253</v>
+        <v>362.2364062294453</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01873104097774832</v>
+        <v>0.2000899948640486</v>
       </c>
       <c r="J4" t="n">
-        <v>-307.9811547772856</v>
+        <v>-178.9966877315872</v>
       </c>
       <c r="K4" t="n">
-        <v>-302.1274236215413</v>
+        <v>-171.1917128572615</v>
       </c>
     </row>
     <row r="5">
@@ -609,159 +609,159 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>X_calc, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9476184290006716</v>
+        <v>0.2443337544890952</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03423563979216381</v>
+        <v>0.1052924746401622</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002409657618925982</v>
+        <v>0.03476216713477132</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04908826355582342</v>
+        <v>0.1864461507641585</v>
       </c>
       <c r="H5" t="n">
-        <v>271.7919564830427</v>
+        <v>1575.185576620525</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01840123163304671</v>
+        <v>0.2525333906476114</v>
       </c>
       <c r="J5" t="n">
-        <v>-309.4700716372012</v>
+        <v>-168.6797330137084</v>
       </c>
       <c r="K5" t="n">
-        <v>-305.5675842000383</v>
+        <v>-162.8260018579641</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>Ridge_w</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>P, T, Plag1</t>
+          <t>X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9052990221656849</v>
+        <v>0.2185721636543644</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03500191050081443</v>
+        <v>0.09005166573630176</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00435643544866426</v>
+        <v>0.03594725212642533</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06600329877107855</v>
+        <v>0.1895976058035157</v>
       </c>
       <c r="H6" t="n">
-        <v>259.8660883615503</v>
+        <v>1079.35819396772</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03295979816435951</v>
+        <v>0.2620914273921884</v>
       </c>
       <c r="J6" t="n">
-        <v>-276.6772579097751</v>
+        <v>-162.9365369533914</v>
       </c>
       <c r="K6" t="n">
-        <v>-270.8235267540308</v>
+        <v>-153.1803183604843</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>elasticnet_w</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P, Plag1, X_calc</t>
+          <t>FS_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8282722573775927</v>
+        <v>0.2063995082547695</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05246073598394848</v>
+        <v>0.09394056409606363</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00789982154976508</v>
+        <v>0.03650721875718122</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08888094030648573</v>
+        <v>0.1910686231624157</v>
       </c>
       <c r="H7" t="n">
-        <v>684.7418288585025</v>
+        <v>1190.357929153007</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05854819787155776</v>
+        <v>0.266635200653596</v>
       </c>
       <c r="J7" t="n">
-        <v>-245.7275856368842</v>
+        <v>-160.1327537165119</v>
       </c>
       <c r="K7" t="n">
-        <v>-239.87385448114</v>
+        <v>-148.4252914050234</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>LASSO_w</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>FS_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7417510664890572</v>
+        <v>0.2034854953572113</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06740423472960835</v>
+        <v>0.0940161763781214</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01187997034724544</v>
+        <v>0.03664126921130639</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1089952767198902</v>
+        <v>0.1914190931211053</v>
       </c>
       <c r="H8" t="n">
-        <v>1097.556805203604</v>
+        <v>1196.673577866255</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08629065929635467</v>
+        <v>0.2676032398407511</v>
       </c>
       <c r="J8" t="n">
-        <v>-228.510875975841</v>
+        <v>-159.9421651859386</v>
       </c>
       <c r="K8" t="n">
-        <v>-226.5596322572596</v>
+        <v>-148.23470287445</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rf_w</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -769,38 +769,38 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>FS_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7143882502389979</v>
+        <v>-0.1617265709999567</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06867649567441483</v>
+        <v>0.1006951732287264</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01313871492848514</v>
+        <v>0.05344175880014546</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1146242336004265</v>
+        <v>0.2311747365093026</v>
       </c>
       <c r="H9" t="n">
-        <v>927.9502745936268</v>
+        <v>711.3247589534063</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09538062537824026</v>
+        <v>0.7728544049201778</v>
       </c>
       <c r="J9" t="n">
-        <v>-223.2739875957616</v>
+        <v>-150.3164676080297</v>
       </c>
       <c r="K9" t="n">
-        <v>-221.3227438771802</v>
+        <v>-148.3652238894483</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>rf_w</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -808,32 +808,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>FS_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.6801001755884444</v>
+        <v>-0.1793408408155817</v>
       </c>
       <c r="E10" t="n">
-        <v>0.08556164177400588</v>
+        <v>0.1003979185562957</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01471603532464256</v>
+        <v>0.05425205063853999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1213096670700343</v>
+        <v>0.2329206960287986</v>
       </c>
       <c r="H10" t="n">
-        <v>1838.478875739901</v>
+        <v>774.6642511214864</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1067711720507165</v>
+        <v>0.7845573753833051</v>
       </c>
       <c r="J10" t="n">
-        <v>-217.378512148551</v>
+        <v>-149.5339533493348</v>
       </c>
       <c r="K10" t="n">
-        <v>-215.4272684299695</v>
+        <v>-147.5827096307533</v>
       </c>
     </row>
   </sheetData>
